--- a/results/Treatment_1965/synth_results_1965.xlsx
+++ b/results/Treatment_1965/synth_results_1965.xlsx
@@ -391,16 +391,16 @@
         <v>1950</v>
       </c>
       <c r="B2">
-        <v>0.0008904109589041096</v>
+        <v>0.0008925109307836388</v>
       </c>
       <c r="C2">
-        <v>0.0008355909308477066</v>
+        <v>0.0008370402896578764</v>
       </c>
       <c r="D2">
-        <v>5.482002805640292E-05</v>
+        <v>5.547064112576235E-05</v>
       </c>
       <c r="E2">
-        <v>6.560629852790292</v>
+        <v>6.626997745644343</v>
       </c>
     </row>
     <row r="3">
@@ -408,16 +408,16 @@
         <v>1951</v>
       </c>
       <c r="B3">
-        <v>0.0005999999999999999</v>
+        <v>0.000601264402394389</v>
       </c>
       <c r="C3">
-        <v>0.0006744017144245101</v>
+        <v>0.000675620739414697</v>
       </c>
       <c r="D3">
-        <v>-7.44017144245102E-05</v>
+        <v>-7.435633702030807E-05</v>
       </c>
       <c r="E3">
-        <v>-11.0322546389135</v>
+        <v>-11.0056326993047</v>
       </c>
     </row>
     <row r="4">
@@ -425,16 +425,16 @@
         <v>1952</v>
       </c>
       <c r="B4">
-        <v>0.0007808219178082191</v>
+        <v>0.0007846351628494586</v>
       </c>
       <c r="C4">
-        <v>0.0009183022370135885</v>
+        <v>0.0009200717789125906</v>
       </c>
       <c r="D4">
-        <v>-0.0001374803192053694</v>
+        <v>-0.000135436616063132</v>
       </c>
       <c r="E4">
-        <v>-14.97114061841658</v>
+        <v>-14.72022283122313</v>
       </c>
     </row>
     <row r="5">
@@ -442,16 +442,16 @@
         <v>1953</v>
       </c>
       <c r="B5">
-        <v>0.0006705479452054794</v>
+        <v>0.0006722818491672769</v>
       </c>
       <c r="C5">
-        <v>0.0008295124644676487</v>
+        <v>0.0008310761524660858</v>
       </c>
       <c r="D5">
-        <v>-0.0001589645192621693</v>
+        <v>-0.0001587943032988089</v>
       </c>
       <c r="E5">
-        <v>-19.16360827250342</v>
+        <v>-19.10707013161335</v>
       </c>
     </row>
     <row r="6">
@@ -459,16 +459,16 @@
         <v>1954</v>
       </c>
       <c r="B6">
-        <v>0.0009657534246575343</v>
+        <v>0.000967773776393036</v>
       </c>
       <c r="C6">
-        <v>0.0008136625888957441</v>
+        <v>0.0008155374738338277</v>
       </c>
       <c r="D6">
-        <v>0.0001520908357617902</v>
+        <v>0.0001522363025592083</v>
       </c>
       <c r="E6">
-        <v>18.69212593001223</v>
+        <v>18.66699047482736</v>
       </c>
     </row>
     <row r="7">
@@ -476,16 +476,16 @@
         <v>1955</v>
       </c>
       <c r="B7">
-        <v>0.0008356164383561644</v>
+        <v>0.0008382239729680177</v>
       </c>
       <c r="C7">
-        <v>0.0007451277490510421</v>
+        <v>0.0007464388584437144</v>
       </c>
       <c r="D7">
-        <v>9.048868930512232E-05</v>
+        <v>9.178511452430328E-05</v>
       </c>
       <c r="E7">
-        <v>12.14405038872385</v>
+        <v>12.2964009022347</v>
       </c>
     </row>
     <row r="8">
@@ -493,16 +493,16 @@
         <v>1956</v>
       </c>
       <c r="B8">
-        <v>0.0006438356164383561</v>
+        <v>0.0006449791045540373</v>
       </c>
       <c r="C8">
-        <v>0.0006969748660737008</v>
+        <v>0.0006979856149788265</v>
       </c>
       <c r="D8">
-        <v>-5.313924963534463E-05</v>
+        <v>-5.300651042478921E-05</v>
       </c>
       <c r="E8">
-        <v>-7.624270575881209</v>
+        <v>-7.594212443246009</v>
       </c>
     </row>
     <row r="9">
@@ -510,16 +510,16 @@
         <v>1957</v>
       </c>
       <c r="B9">
-        <v>0.0008013698630136986</v>
+        <v>0.0008024510361586724</v>
       </c>
       <c r="C9">
-        <v>0.0007165597384189443</v>
+        <v>0.0007179686099999164</v>
       </c>
       <c r="D9">
-        <v>8.481012459475427E-05</v>
+        <v>8.448242615875605E-05</v>
       </c>
       <c r="E9">
-        <v>11.83573679172707</v>
+        <v>11.76686904999452</v>
       </c>
     </row>
     <row r="10">
@@ -527,16 +527,16 @@
         <v>1958</v>
       </c>
       <c r="B10">
-        <v>0.0007876712328767123</v>
+        <v>0.0007880953588970963</v>
       </c>
       <c r="C10">
-        <v>0.0007632248797882082</v>
+        <v>0.0007643969797121329</v>
       </c>
       <c r="D10">
-        <v>2.444635308850409E-05</v>
+        <v>2.369837918496343E-05</v>
       </c>
       <c r="E10">
-        <v>3.203034090724068</v>
+        <v>3.100271169816513</v>
       </c>
     </row>
     <row r="11">
@@ -544,16 +544,16 @@
         <v>1959</v>
       </c>
       <c r="B11">
-        <v>0.0005897260273972603</v>
+        <v>0.0005910850529475994</v>
       </c>
       <c r="C11">
-        <v>0.0007168886702816142</v>
+        <v>0.0007180482347542853</v>
       </c>
       <c r="D11">
-        <v>-0.0001271626428843539</v>
+        <v>-0.0001269631818066859</v>
       </c>
       <c r="E11">
-        <v>-17.73812980394862</v>
+        <v>-17.68170655696027</v>
       </c>
     </row>
     <row r="12">
@@ -561,16 +561,16 @@
         <v>1960</v>
       </c>
       <c r="B12">
-        <v>0.0009041095890410959</v>
+        <v>0.0009027991600581399</v>
       </c>
       <c r="C12">
-        <v>0.000841768074848185</v>
+        <v>0.0008427958038784984</v>
       </c>
       <c r="D12">
-        <v>6.234151419291095E-05</v>
+        <v>6.000335617964154E-05</v>
       </c>
       <c r="E12">
-        <v>7.406020263260092</v>
+        <v>7.119560385031523</v>
       </c>
     </row>
     <row r="13">
@@ -578,16 +578,16 @@
         <v>1961</v>
       </c>
       <c r="B13">
-        <v>0.0004068493150684931</v>
+        <v>0.0004079966728743662</v>
       </c>
       <c r="C13">
-        <v>0.0009168024778013846</v>
+        <v>0.0009189239250189165</v>
       </c>
       <c r="D13">
-        <v>-0.0005099531627328915</v>
+        <v>-0.0005109272521445502</v>
       </c>
       <c r="E13">
-        <v>-55.62301314409922</v>
+        <v>-55.60060394923688</v>
       </c>
     </row>
     <row r="14">
@@ -595,16 +595,16 @@
         <v>1962</v>
       </c>
       <c r="B14">
-        <v>0.0008013698630136986</v>
+        <v>0.0008004313946064571</v>
       </c>
       <c r="C14">
-        <v>0.0009740293368274218</v>
+        <v>0.0009757241770774013</v>
       </c>
       <c r="D14">
-        <v>-0.0001726594738137232</v>
+        <v>-0.0001752927824709442</v>
       </c>
       <c r="E14">
-        <v>-17.72631144520803</v>
+        <v>-17.96540319375921</v>
       </c>
     </row>
     <row r="15">
@@ -612,16 +612,16 @@
         <v>1963</v>
       </c>
       <c r="B15">
-        <v>0.0009863013698630137</v>
+        <v>0.000987215592526939</v>
       </c>
       <c r="C15">
-        <v>0.0008367331135253181</v>
+        <v>0.0008384421132367125</v>
       </c>
       <c r="D15">
-        <v>0.0001495682563376955</v>
+        <v>0.0001487734792902265</v>
       </c>
       <c r="E15">
-        <v>17.87526439673644</v>
+        <v>17.74403705890953</v>
       </c>
     </row>
     <row r="16">
@@ -629,16 +629,16 @@
         <v>1964</v>
       </c>
       <c r="B16">
-        <v>0.0009315068493150684</v>
+        <v>0.0009362134403533977</v>
       </c>
       <c r="C16">
-        <v>0.0008965814485979373</v>
+        <v>0.0008983850320484962</v>
       </c>
       <c r="D16">
-        <v>3.492540071713113E-05</v>
+        <v>3.782840830490156E-05</v>
       </c>
       <c r="E16">
-        <v>3.895396315833551</v>
+        <v>4.210712217527186</v>
       </c>
     </row>
     <row r="17">
@@ -646,16 +646,16 @@
         <v>1965</v>
       </c>
       <c r="B17">
-        <v>0.0006465753424657534</v>
+        <v>0.0006482096531711096</v>
       </c>
       <c r="C17">
-        <v>0.0007931370701611223</v>
+        <v>0.000794538964165293</v>
       </c>
       <c r="D17">
-        <v>-0.0001465617276953689</v>
+        <v>-0.0001463293109941834</v>
       </c>
       <c r="E17">
-        <v>-18.47873882197885</v>
+        <v>-18.41688294644057</v>
       </c>
     </row>
     <row r="18">
@@ -663,16 +663,16 @@
         <v>1966</v>
       </c>
       <c r="B18">
-        <v>0.0009246575342465753</v>
+        <v>0.0009283755558689517</v>
       </c>
       <c r="C18">
-        <v>0.0008153424179327476</v>
+        <v>0.0008165187679275919</v>
       </c>
       <c r="D18">
-        <v>0.0001093151163138277</v>
+        <v>0.0001118567879413599</v>
       </c>
       <c r="E18">
-        <v>13.40726471596924</v>
+        <v>13.69923048128628</v>
       </c>
     </row>
     <row r="19">
@@ -680,16 +680,16 @@
         <v>1967</v>
       </c>
       <c r="B19">
-        <v>0.0006917808219178081</v>
+        <v>0.0006951670355747701</v>
       </c>
       <c r="C19">
-        <v>0.0007928490669428899</v>
+        <v>0.0007939774280938277</v>
       </c>
       <c r="D19">
-        <v>-0.0001010682450250818</v>
+        <v>-9.881039251905758E-05</v>
       </c>
       <c r="E19">
-        <v>-12.74747606310318</v>
+        <v>-12.44498760579132</v>
       </c>
     </row>
     <row r="20">
@@ -697,16 +697,16 @@
         <v>1968</v>
       </c>
       <c r="B20">
-        <v>0.001143835616438356</v>
+        <v>0.00114463838799432</v>
       </c>
       <c r="C20">
-        <v>0.0008537719023191022</v>
+        <v>0.0008551071934074526</v>
       </c>
       <c r="D20">
-        <v>0.0002900637141192539</v>
+        <v>0.0002895311945868673</v>
       </c>
       <c r="E20">
-        <v>33.97438043244961</v>
+        <v>33.85905262159427</v>
       </c>
     </row>
     <row r="21">
@@ -714,16 +714,16 @@
         <v>1969</v>
       </c>
       <c r="B21">
-        <v>0.000726027397260274</v>
+        <v>0.0007279888169643569</v>
       </c>
       <c r="C21">
-        <v>0.0007390533582701745</v>
+        <v>0.0007400322833353792</v>
       </c>
       <c r="D21">
-        <v>-1.302596100990051E-05</v>
+        <v>-1.204346637102231E-05</v>
       </c>
       <c r="E21">
-        <v>-1.762519696871283</v>
+        <v>-1.62742445731442</v>
       </c>
     </row>
     <row r="22">
@@ -731,16 +731,16 @@
         <v>1970</v>
       </c>
       <c r="B22">
-        <v>0.001465753424657534</v>
+        <v>0.001468158884709429</v>
       </c>
       <c r="C22">
-        <v>0.0008504506552392986</v>
+        <v>0.0008517160747337413</v>
       </c>
       <c r="D22">
-        <v>0.0006153027694182356</v>
+        <v>0.0006164428099756879</v>
       </c>
       <c r="E22">
-        <v>72.35020228717475</v>
+        <v>72.37656165740405</v>
       </c>
     </row>
     <row r="23">
@@ -748,16 +748,16 @@
         <v>1971</v>
       </c>
       <c r="B23">
-        <v>0.0008561643835616438</v>
+        <v>0.0008588278038813216</v>
       </c>
       <c r="C23">
-        <v>0.0007981723405596225</v>
+        <v>0.0007993860306626271</v>
       </c>
       <c r="D23">
-        <v>5.799204300202131E-05</v>
+        <v>5.944177321869451E-05</v>
       </c>
       <c r="E23">
-        <v>7.265604187857644</v>
+        <v>7.435928442409987</v>
       </c>
     </row>
     <row r="24">
@@ -765,16 +765,16 @@
         <v>1972</v>
       </c>
       <c r="B24">
-        <v>0.0007602739726027397</v>
+        <v>0.0007637643751805284</v>
       </c>
       <c r="C24">
-        <v>0.000745784183022279</v>
+        <v>0.0007465338260390037</v>
       </c>
       <c r="D24">
-        <v>1.448978958046071E-05</v>
+        <v>1.72305491415247E-05</v>
       </c>
       <c r="E24">
-        <v>1.942893119795201</v>
+        <v>2.308073464393088</v>
       </c>
     </row>
     <row r="25">
@@ -782,16 +782,16 @@
         <v>1973</v>
       </c>
       <c r="B25">
-        <v>0.0007397260273972603</v>
+        <v>0.0007418358803387</v>
       </c>
       <c r="C25">
-        <v>0.0006842150272766154</v>
+        <v>0.0006849908029066621</v>
       </c>
       <c r="D25">
-        <v>5.551100012064487E-05</v>
+        <v>5.684507743203792E-05</v>
       </c>
       <c r="E25">
-        <v>8.113092800898512</v>
+        <v>8.298662871212844</v>
       </c>
     </row>
   </sheetData>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.7360834219936057</v>
+        <v>0.7365489300017228</v>
       </c>
     </row>
     <row r="3">
@@ -833,27 +833,27 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2485147423635291</v>
+        <v>0.249206042798717</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Julius Evola</t>
+          <t>Oswald Spengler</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.001918767791972359</v>
+        <v>0.001007058781263252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oswald Spengler</t>
+          <t>Julius Evola</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.0009750437113658498</v>
+        <v>0.0008679979517399203</v>
       </c>
     </row>
     <row r="6">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.0001212695788713747</v>
+        <v>0.0001207204755605262</v>
       </c>
     </row>
     <row r="7">
@@ -873,87 +873,87 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.0001205369242533974</v>
+        <v>0.0001202973612443845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Machiavelli</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.0001177320280241052</v>
+        <v>0.0001180122379715632</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machiavelli</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.0001173817331958572</v>
+        <v>0.0001166285528832131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hobbes</t>
+          <t>Plutarch</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.0001154118191665336</v>
+        <v>0.0001146479105537293</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Adam Smith</t>
+          <t>Hobbes</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.000114363851411009</v>
+        <v>0.0001145716640547133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Herodotus</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.0001137992992946528</v>
+        <v>0.0001135267724110355</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Plutarch</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.000113649432547783</v>
+        <v>0.0001130181366661651</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>Adam Smith</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.0001129499072398392</v>
+        <v>0.000112651219181129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.0001126490453960595</v>
+        <v>0.0001123207492241278</v>
       </c>
     </row>
     <row r="16">
@@ -963,67 +963,67 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.0001126312689603598</v>
+        <v>0.0001117559888526889</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alexander Hamilton</t>
+          <t>Thucydides</t>
         </is>
       </c>
       <c r="B17">
-        <v>0.0001116020935714137</v>
+        <v>0.000109357402990949</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Malthus</t>
+          <t>Pericles</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.0001109527351605286</v>
+        <v>0.0001092324274726379</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Thucydides</t>
+          <t>Alexander Hamilton</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.0001087065607818532</v>
+        <v>0.0001092177545493691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pericles</t>
+          <t>Malthus</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.0001085659707007055</v>
+        <v>0.0001090673400613051</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>William Penn</t>
+          <t>Thomas More</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.000107224524593298</v>
+        <v>0.0001056378832662383</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Thomas More</t>
+          <t>William Penn</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.0001068103705298846</v>
+        <v>0.0001048956660567468</v>
       </c>
     </row>
     <row r="23">
@@ -1033,27 +1033,27 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.0001027415843159724</v>
+        <v>0.0001024784052528079</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Mazzini</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.0001010215019294896</v>
+        <v>9.899925260849191E-05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mazzini</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B25">
-        <v>9.930207838689625E-05</v>
+        <v>9.853565785740266E-05</v>
       </c>
     </row>
     <row r="26">
@@ -1063,27 +1063,27 @@
         </is>
       </c>
       <c r="B26">
-        <v>9.782084848336817E-05</v>
+        <v>9.784618951700581E-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Aquinas</t>
         </is>
       </c>
       <c r="B27">
-        <v>9.584566843812893E-05</v>
+        <v>9.600821320574083E-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tocqueville</t>
+          <t>Spinoza</t>
         </is>
       </c>
       <c r="B28">
-        <v>9.565902136356413E-05</v>
+        <v>9.577459718609148E-05</v>
       </c>
     </row>
     <row r="29">
@@ -1093,77 +1093,77 @@
         </is>
       </c>
       <c r="B29">
-        <v>9.541705495334806E-05</v>
+        <v>9.531988451299868E-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aquinas</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="B30">
-        <v>9.522297614416229E-05</v>
+        <v>9.42389847517441E-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Spinoza</t>
+          <t>Tocqueville</t>
         </is>
       </c>
       <c r="B31">
-        <v>9.504472718440414E-05</v>
+        <v>9.391782726908902E-05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>John Stuart Mill</t>
+          <t>Marlowe</t>
         </is>
       </c>
       <c r="B32">
-        <v>9.441017512975472E-05</v>
+        <v>9.35699506088334E-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marlowe</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B33">
-        <v>9.355383263432365E-05</v>
+        <v>9.334325100615286E-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Henry George</t>
+          <t>John Stuart Mill</t>
         </is>
       </c>
       <c r="B34">
-        <v>9.350537614884923E-05</v>
+        <v>9.170771868139591E-05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Faraday</t>
         </is>
       </c>
       <c r="B35">
-        <v>9.349875016672281E-05</v>
+        <v>9.169866003985627E-05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Faraday</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B36">
-        <v>9.141861052177834E-05</v>
+        <v>9.133349834564894E-05</v>
       </c>
     </row>
     <row r="37">
@@ -1173,57 +1173,57 @@
         </is>
       </c>
       <c r="B37">
-        <v>9.081600311722412E-05</v>
+        <v>9.130656137170626E-05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Euripides</t>
         </is>
       </c>
       <c r="B38">
-        <v>9.0474856136441E-05</v>
+        <v>9.128096326047888E-05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Euripides</t>
+          <t>Sophocles</t>
         </is>
       </c>
       <c r="B39">
-        <v>9.002445622579674E-05</v>
+        <v>9.113355234536723E-05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sophocles</t>
+          <t>Henry George</t>
         </is>
       </c>
       <c r="B40">
-        <v>8.987399413760705E-05</v>
+        <v>9.089434404777862E-05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Oscar Wilde</t>
+          <t>Pasteur</t>
         </is>
       </c>
       <c r="B41">
-        <v>8.896342326155061E-05</v>
+        <v>8.853282503232266E-05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pasteur</t>
+          <t>Descartes</t>
         </is>
       </c>
       <c r="B42">
-        <v>8.84912487303279E-05</v>
+        <v>8.76865736133228E-05</v>
       </c>
     </row>
     <row r="43">
@@ -1233,57 +1233,57 @@
         </is>
       </c>
       <c r="B43">
-        <v>8.770354074122602E-05</v>
+        <v>8.760968003404773E-05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>John Milton</t>
+          <t>Helmholtz</t>
         </is>
       </c>
       <c r="B44">
-        <v>8.759850699851703E-05</v>
+        <v>8.681141051573242E-05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Descartes</t>
+          <t>Herder</t>
         </is>
       </c>
       <c r="B45">
-        <v>8.741044802206051E-05</v>
+        <v>8.66847259007273E-05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Herbert Spencer</t>
+          <t>Copernicus</t>
         </is>
       </c>
       <c r="B46">
-        <v>8.648765838619439E-05</v>
+        <v>8.650271282698634E-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Copernicus</t>
+          <t>Oscar Wilde</t>
         </is>
       </c>
       <c r="B47">
-        <v>8.61269815923535E-05</v>
+        <v>8.625874703415367E-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Helmholtz</t>
+          <t>Aristophanes</t>
         </is>
       </c>
       <c r="B48">
-        <v>8.601431494753843E-05</v>
+        <v>8.598860716013833E-05</v>
       </c>
     </row>
     <row r="49">
@@ -1293,167 +1293,167 @@
         </is>
       </c>
       <c r="B49">
-        <v>8.593762110998605E-05</v>
+        <v>8.573757425951572E-05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Herder</t>
+          <t>Aeschylus</t>
         </is>
       </c>
       <c r="B50">
-        <v>8.590810046177222E-05</v>
+        <v>8.542037118042244E-05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Edmund Burke</t>
+          <t>John Milton</t>
         </is>
       </c>
       <c r="B51">
-        <v>8.505125110214472E-05</v>
+        <v>8.479998186149734E-05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Aristophanes</t>
+          <t>Rilke</t>
         </is>
       </c>
       <c r="B52">
-        <v>8.486743056054605E-05</v>
+        <v>8.382567770888144E-05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aeschylus</t>
+          <t>Herbert Spencer</t>
         </is>
       </c>
       <c r="B53">
-        <v>8.431906138429548E-05</v>
+        <v>8.381366615389923E-05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Martin Luther</t>
         </is>
       </c>
       <c r="B54">
-        <v>8.323041232671265E-05</v>
+        <v>8.255939915783346E-05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oliver Wendell Holmes</t>
+          <t>Edmund Burke</t>
         </is>
       </c>
       <c r="B55">
-        <v>8.320606145285289E-05</v>
+        <v>8.229910576903937E-05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Rilke</t>
+          <t>Cicero</t>
         </is>
       </c>
       <c r="B56">
-        <v>8.314385308728559E-05</v>
+        <v>8.214052112935703E-05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Martin Luther</t>
+          <t>Montaigne</t>
         </is>
       </c>
       <c r="B57">
-        <v>8.196747262947021E-05</v>
+        <v>8.152643700330831E-05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Walt Whitman</t>
+          <t>Chaucer</t>
         </is>
       </c>
       <c r="B58">
-        <v>8.178302649599481E-05</v>
+        <v>8.150357162902964E-05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cicero</t>
+          <t>Walt Whitman</t>
         </is>
       </c>
       <c r="B59">
-        <v>8.178120015668036E-05</v>
+        <v>8.130400840125252E-05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Montaigne</t>
+          <t>Oliver Wendell Holmes</t>
         </is>
       </c>
       <c r="B60">
-        <v>8.170028994712754E-05</v>
+        <v>8.050832314432369E-05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Proudhon</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="B61">
-        <v>8.148535483398046E-05</v>
+        <v>8.048533269752975E-05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Chaucer</t>
+          <t>Proudhon</t>
         </is>
       </c>
       <c r="B62">
-        <v>8.116685344251985E-05</v>
+        <v>7.965272290100206E-05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Renan</t>
+          <t>Hippocrates</t>
         </is>
       </c>
       <c r="B63">
-        <v>7.894260944664059E-05</v>
+        <v>7.924538590985281E-05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hippocrates</t>
+          <t>Virgil</t>
         </is>
       </c>
       <c r="B64">
-        <v>7.826521110652592E-05</v>
+        <v>7.892923568310026E-05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Virgil</t>
+          <t>Renan</t>
         </is>
       </c>
       <c r="B65">
-        <v>7.817727377910347E-05</v>
+        <v>7.720148868526074E-05</v>
       </c>
     </row>
     <row r="66">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>7.634635913054448E-05</v>
+        <v>7.672038456850434E-05</v>
       </c>
     </row>
     <row r="67">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B67">
-        <v>7.550729211631017E-05</v>
+        <v>7.592473020215089E-05</v>
       </c>
     </row>
     <row r="68">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="B68">
-        <v>7.461606288817299E-05</v>
+        <v>7.408684681820122E-05</v>
       </c>
     </row>
     <row r="69">
@@ -1493,17 +1493,17 @@
         </is>
       </c>
       <c r="B69">
-        <v>7.401071655608491E-05</v>
+        <v>7.344905569527002E-05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bakunin</t>
+          <t>Max Weber</t>
         </is>
       </c>
       <c r="B70">
-        <v>7.301673931468066E-05</v>
+        <v>7.255634558086403E-05</v>
       </c>
     </row>
     <row r="71">
@@ -1513,27 +1513,27 @@
         </is>
       </c>
       <c r="B71">
-        <v>7.270492891045982E-05</v>
+        <v>7.236022293180833E-05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Max Weber</t>
+          <t>Lord Byron</t>
         </is>
       </c>
       <c r="B72">
-        <v>7.225638188238203E-05</v>
+        <v>7.158984519825671E-05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lord Byron</t>
+          <t>Bakunin</t>
         </is>
       </c>
       <c r="B73">
-        <v>7.215860850439213E-05</v>
+        <v>7.125595785553289E-05</v>
       </c>
     </row>
     <row r="74">
@@ -1543,47 +1543,47 @@
         </is>
       </c>
       <c r="B74">
-        <v>6.930093037355601E-05</v>
+        <v>7.015106216895905E-05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alexander Pope</t>
+          <t>Victor Hugo</t>
         </is>
       </c>
       <c r="B75">
-        <v>6.907339900257074E-05</v>
+        <v>6.829223922598971E-05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Victor Hugo</t>
+          <t>Malory</t>
         </is>
       </c>
       <c r="B76">
-        <v>6.860960789556298E-05</v>
+        <v>6.793773460417799E-05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Malory</t>
+          <t>Marcus Aurelius</t>
         </is>
       </c>
       <c r="B77">
-        <v>6.852419364652721E-05</v>
+        <v>6.766577231737737E-05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Robert Owen</t>
+          <t>Alexander Pope</t>
         </is>
       </c>
       <c r="B78">
-        <v>6.844395175410499E-05</v>
+        <v>6.664799855053836E-05</v>
       </c>
     </row>
     <row r="79">
@@ -1593,77 +1593,77 @@
         </is>
       </c>
       <c r="B79">
-        <v>6.708602802863366E-05</v>
+        <v>6.648389371002621E-05</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Marcus Aurelius</t>
+          <t>Schleiermacher</t>
         </is>
       </c>
       <c r="B80">
-        <v>6.694321513726618E-05</v>
+        <v>6.621783779540696E-05</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Schleiermacher</t>
+          <t>Robert Owen</t>
         </is>
       </c>
       <c r="B81">
-        <v>6.611762992837199E-05</v>
+        <v>6.606689033538795E-05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Charles Darwin</t>
+          <t>Ranke</t>
         </is>
       </c>
       <c r="B82">
-        <v>6.591644502047777E-05</v>
+        <v>6.545986259520735E-05</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Froissart</t>
+          <t>Aesop</t>
         </is>
       </c>
       <c r="B83">
-        <v>6.587452325932519E-05</v>
+        <v>6.545846888632902E-05</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ranke</t>
+          <t>Charles Darwin</t>
         </is>
       </c>
       <c r="B84">
-        <v>6.531352509669447E-05</v>
+        <v>6.531678292101266E-05</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aesop</t>
+          <t>Froissart</t>
         </is>
       </c>
       <c r="B85">
-        <v>6.477948259245634E-05</v>
+        <v>6.428631958423383E-05</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Jonathan Swift</t>
+          <t>Wundt</t>
         </is>
       </c>
       <c r="B86">
-        <v>6.473609006789909E-05</v>
+        <v>6.40117372632637E-05</v>
       </c>
     </row>
     <row r="87">
@@ -1673,17 +1673,17 @@
         </is>
       </c>
       <c r="B87">
-        <v>6.42412254133422E-05</v>
+        <v>6.367106266726693E-05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Wundt</t>
+          <t>Jonathan Swift</t>
         </is>
       </c>
       <c r="B88">
-        <v>6.389453998978743E-05</v>
+        <v>6.242313279124962E-05</v>
       </c>
     </row>
     <row r="89">
@@ -1693,67 +1693,67 @@
         </is>
       </c>
       <c r="B89">
-        <v>6.256427134985345E-05</v>
+        <v>6.201624940118181E-05</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Robert Browning</t>
+          <t>Cellini</t>
         </is>
       </c>
       <c r="B90">
-        <v>6.143681239994696E-05</v>
+        <v>6.182496272490378E-05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cellini</t>
+          <t>Robert Browning</t>
         </is>
       </c>
       <c r="B91">
-        <v>6.143646992951632E-05</v>
+        <v>6.08841713243647E-05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Thomas Carlyle</t>
+          <t>John Knox</t>
         </is>
       </c>
       <c r="B92">
-        <v>6.141271637074197E-05</v>
+        <v>6.076649707954645E-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>John Knox</t>
+          <t>Robert Burns</t>
         </is>
       </c>
       <c r="B93">
-        <v>6.136508278748984E-05</v>
+        <v>6.073230799350276E-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Robert Burns</t>
+          <t>Molière</t>
         </is>
       </c>
       <c r="B94">
-        <v>6.13207659985355E-05</v>
+        <v>6.055123239885616E-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Molière</t>
+          <t>Dilthey</t>
         </is>
       </c>
       <c r="B95">
-        <v>6.089348740905456E-05</v>
+        <v>6.053195167324239E-05</v>
       </c>
     </row>
     <row r="96">
@@ -1763,27 +1763,27 @@
         </is>
       </c>
       <c r="B96">
-        <v>6.059179476728832E-05</v>
+        <v>6.000182831113909E-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Dilthey</t>
+          <t>Simmel</t>
         </is>
       </c>
       <c r="B97">
-        <v>6.056888003005995E-05</v>
+        <v>5.954040754328933E-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>John Ruskin</t>
+          <t>Thomas Carlyle</t>
         </is>
       </c>
       <c r="B98">
-        <v>5.991089557811397E-05</v>
+        <v>5.930175762027192E-05</v>
       </c>
     </row>
     <row r="99">
@@ -1793,57 +1793,57 @@
         </is>
       </c>
       <c r="B99">
-        <v>5.965904835556596E-05</v>
+        <v>5.823356608498668E-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Simmel</t>
+          <t>Thomas Browne</t>
         </is>
       </c>
       <c r="B100">
-        <v>5.965553171623093E-05</v>
+        <v>5.787771746389131E-05</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Thomas Browne</t>
+          <t>John Ruskin</t>
         </is>
       </c>
       <c r="B101">
-        <v>5.843115589560972E-05</v>
+        <v>5.78034718460952E-05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Frederick Douglass</t>
+          <t>Epictetus</t>
         </is>
       </c>
       <c r="B102">
-        <v>5.675501287592518E-05</v>
+        <v>5.66753814771813E-05</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Epictetus</t>
+          <t>Clausewitz</t>
         </is>
       </c>
       <c r="B103">
-        <v>5.622342732801388E-05</v>
+        <v>5.595798722918387E-05</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Clausewitz</t>
+          <t>John Calvin</t>
         </is>
       </c>
       <c r="B104">
-        <v>5.617117000386242E-05</v>
+        <v>5.561672638675639E-05</v>
       </c>
     </row>
     <row r="105">
@@ -1853,37 +1853,37 @@
         </is>
       </c>
       <c r="B105">
-        <v>5.581754962942879E-05</v>
+        <v>5.558372040737486E-05</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>John Calvin</t>
+          <t>Hamann</t>
         </is>
       </c>
       <c r="B106">
-        <v>5.577846605949171E-05</v>
+        <v>5.50710382807937E-05</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Talcott Parsons</t>
+          <t>Frederick Douglass</t>
         </is>
       </c>
       <c r="B107">
-        <v>5.537520003112735E-05</v>
+        <v>5.483659841081716E-05</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Hamann</t>
+          <t>Talcott Parsons</t>
         </is>
       </c>
       <c r="B108">
-        <v>5.527564482307171E-05</v>
+        <v>5.474664944755373E-05</v>
       </c>
     </row>
     <row r="109">
@@ -1893,87 +1893,87 @@
         </is>
       </c>
       <c r="B109">
-        <v>5.439973204478496E-05</v>
+        <v>5.416085926511822E-05</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sombart</t>
+          <t>Kempis</t>
         </is>
       </c>
       <c r="B110">
-        <v>5.354557491797549E-05</v>
+        <v>5.317841738876273E-05</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kempis</t>
+          <t>William Harvey</t>
         </is>
       </c>
       <c r="B111">
-        <v>5.335413210686568E-05</v>
+        <v>5.207911042698081E-05</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>John Bunyan</t>
         </is>
       </c>
       <c r="B112">
-        <v>5.289285568762276E-05</v>
+        <v>5.183573561062257E-05</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>John Bunyan</t>
+          <t>Sombart</t>
         </is>
       </c>
       <c r="B113">
-        <v>5.238860664625266E-05</v>
+        <v>5.129423851470378E-05</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>William Harvey</t>
+          <t>William Wordsworth</t>
         </is>
       </c>
       <c r="B114">
-        <v>5.233851565586602E-05</v>
+        <v>5.11420738053196E-05</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Edmund Spenser</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="B115">
-        <v>5.208934281115625E-05</v>
+        <v>5.110212231463786E-05</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>William Wordsworth</t>
+          <t>Scheler</t>
         </is>
       </c>
       <c r="B116">
-        <v>5.172026193775751E-05</v>
+        <v>5.080937227317819E-05</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Scheler</t>
+          <t>Edmund Spenser</t>
         </is>
       </c>
       <c r="B117">
-        <v>5.122550901844541E-05</v>
+        <v>5.036364933919153E-05</v>
       </c>
     </row>
     <row r="118">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B118">
-        <v>5.027040818518913E-05</v>
+        <v>4.971622823030173E-05</v>
       </c>
     </row>
     <row r="119">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="B119">
-        <v>5.015356215931861E-05</v>
+        <v>4.95915192731803E-05</v>
       </c>
     </row>
     <row r="120">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="B120">
-        <v>4.958604406637243E-05</v>
+        <v>4.905354043150396E-05</v>
       </c>
     </row>
     <row r="121">
@@ -2013,27 +2013,27 @@
         </is>
       </c>
       <c r="B121">
-        <v>4.934046781376642E-05</v>
+        <v>4.87942716567372E-05</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Blanqui</t>
+          <t>Auguste Comte</t>
         </is>
       </c>
       <c r="B122">
-        <v>4.921005115267029E-05</v>
+        <v>4.820384060816382E-05</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Auguste Comte</t>
+          <t>Blanqui</t>
         </is>
       </c>
       <c r="B123">
-        <v>4.854242168152035E-05</v>
+        <v>4.796942892596498E-05</v>
       </c>
     </row>
     <row r="124">
@@ -2043,37 +2043,37 @@
         </is>
       </c>
       <c r="B124">
-        <v>4.844365019698642E-05</v>
+        <v>4.729616109014374E-05</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>William Caxton</t>
+          <t>Dante Alighieri</t>
         </is>
       </c>
       <c r="B125">
-        <v>4.647139896169606E-05</v>
+        <v>4.632306654087158E-05</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Dante Alighieri</t>
+          <t>William Caxton</t>
         </is>
       </c>
       <c r="B126">
-        <v>4.629948212997454E-05</v>
+        <v>4.596987497128362E-05</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Wollstonecraft</t>
+          <t>Augustine</t>
         </is>
       </c>
       <c r="B127">
-        <v>4.582991129638664E-05</v>
+        <v>4.537022358608721E-05</v>
       </c>
     </row>
     <row r="128">
@@ -2083,47 +2083,47 @@
         </is>
       </c>
       <c r="B128">
-        <v>4.572188830449582E-05</v>
+        <v>4.512283184750264E-05</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>William Godwin</t>
+          <t>Ebbinghaus</t>
         </is>
       </c>
       <c r="B129">
-        <v>4.548979570397731E-05</v>
+        <v>4.447626841818828E-05</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Ebbinghaus</t>
+          <t>Wollstonecraft</t>
         </is>
       </c>
       <c r="B130">
-        <v>4.506320026778714E-05</v>
+        <v>4.445050259255336E-05</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Augustine</t>
+          <t>Percy Bysshe Shelley</t>
         </is>
       </c>
       <c r="B131">
-        <v>4.496936761404697E-05</v>
+        <v>4.425037357131008E-05</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Percy Bysshe Shelley</t>
+          <t>William Godwin</t>
         </is>
       </c>
       <c r="B132">
-        <v>4.477301062127386E-05</v>
+        <v>4.409731334971163E-05</v>
       </c>
     </row>
     <row r="133">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="B133">
-        <v>4.401368783556464E-05</v>
+        <v>4.33561001038575E-05</v>
       </c>
     </row>
     <row r="134">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B134">
-        <v>4.381229022431784E-05</v>
+        <v>4.315109210068878E-05</v>
       </c>
     </row>
     <row r="135">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B135">
-        <v>4.344644569071307E-05</v>
+        <v>4.278365876798647E-05</v>
       </c>
     </row>
     <row r="136">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="B136">
-        <v>4.322136782488421E-05</v>
+        <v>4.271036167640315E-05</v>
       </c>
     </row>
     <row r="137">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B137">
-        <v>4.318561221248585E-05</v>
+        <v>4.194021199976602E-05</v>
       </c>
     </row>
     <row r="138">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="B138">
-        <v>4.286171393281523E-05</v>
+        <v>4.190805995591309E-05</v>
       </c>
     </row>
     <row r="139">
@@ -2193,117 +2193,117 @@
         </is>
       </c>
       <c r="B139">
-        <v>4.214720545159644E-05</v>
+        <v>4.166579369995191E-05</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Philip Nichols</t>
+          <t>Pierre Corneille</t>
         </is>
       </c>
       <c r="B140">
-        <v>4.211312434607527E-05</v>
+        <v>4.166209759739909E-05</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Pierre Corneille</t>
+          <t>Philip Nichols</t>
         </is>
       </c>
       <c r="B141">
-        <v>4.194915502661765E-05</v>
+        <v>4.163172010458413E-05</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Joseph Lister</t>
+          <t>Jean Racine</t>
         </is>
       </c>
       <c r="B142">
-        <v>4.158500625783822E-05</v>
+        <v>4.129264406461817E-05</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Jean Racine</t>
+          <t>Bigges</t>
         </is>
       </c>
       <c r="B143">
-        <v>4.158161653981857E-05</v>
+        <v>4.109465163243858E-05</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Bigges</t>
+          <t>Joseph Lister</t>
         </is>
       </c>
       <c r="B144">
-        <v>4.156227426445114E-05</v>
+        <v>4.107498083924286E-05</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>John Woolman</t>
+          <t>Ambroise Paré</t>
         </is>
       </c>
       <c r="B145">
-        <v>4.149345602544313E-05</v>
+        <v>4.08680975159028E-05</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Friedrich Schiller</t>
+          <t>Pliny the Younger</t>
         </is>
       </c>
       <c r="B146">
-        <v>4.12758204389043E-05</v>
+        <v>4.077366150533308E-05</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Grimmelshausen</t>
+          <t>Friedrich Schiller</t>
         </is>
       </c>
       <c r="B147">
-        <v>4.127174941623192E-05</v>
+        <v>4.055305445727889E-05</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Pliny the Younger</t>
+          <t>Grimmelshausen</t>
         </is>
       </c>
       <c r="B148">
-        <v>4.122359278778972E-05</v>
+        <v>4.052973428311537E-05</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ambroise Paré</t>
+          <t>Francis Pretty</t>
         </is>
       </c>
       <c r="B149">
-        <v>4.115068951988619E-05</v>
+        <v>4.046631404573365E-05</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Francis Pretty</t>
+          <t>Edward Haies</t>
         </is>
       </c>
       <c r="B150">
-        <v>4.093193293161319E-05</v>
+        <v>4.039851938544042E-05</v>
       </c>
     </row>
     <row r="151">
@@ -2313,17 +2313,17 @@
         </is>
       </c>
       <c r="B151">
-        <v>4.08701665201108E-05</v>
+        <v>4.036887645619909E-05</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Edward Haies</t>
+          <t>John Woolman</t>
         </is>
       </c>
       <c r="B152">
-        <v>4.08640153317979E-05</v>
+        <v>4.032324435336922E-05</v>
       </c>
     </row>
     <row r="153">
@@ -2333,67 +2333,67 @@
         </is>
       </c>
       <c r="B153">
-        <v>4.069203826919822E-05</v>
+        <v>3.978352544209315E-05</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Edward Bellamy</t>
+          <t>Pedro Calderón de la Barca</t>
         </is>
       </c>
       <c r="B154">
-        <v>4.051288928474992E-05</v>
+        <v>3.95770745012061E-05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Pedro Calderón de la Barca</t>
+          <t>Edward Bellamy</t>
         </is>
       </c>
       <c r="B155">
-        <v>4.014222642194435E-05</v>
+        <v>3.935183238814512E-05</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Bastiat</t>
+          <t>Hippolyte Taine</t>
         </is>
       </c>
       <c r="B156">
-        <v>3.981223951957499E-05</v>
+        <v>3.932896508848715E-05</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Hippolyte Taine</t>
+          <t>Alessandro Manzoni</t>
         </is>
       </c>
       <c r="B157">
-        <v>3.963465422577177E-05</v>
+        <v>3.89962804223138E-05</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Robert Merton</t>
+          <t>Bastiat</t>
         </is>
       </c>
       <c r="B158">
-        <v>3.94659753633259E-05</v>
+        <v>3.896728243514374E-05</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Gotthold Ephraim Lessing</t>
+          <t>Robert Merton</t>
         </is>
       </c>
       <c r="B159">
-        <v>3.934710801079116E-05</v>
+        <v>3.895984524266502E-05</v>
       </c>
     </row>
     <row r="160">
@@ -2403,27 +2403,27 @@
         </is>
       </c>
       <c r="B160">
-        <v>3.931896953187471E-05</v>
+        <v>3.88301711248794E-05</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Alessandro Manzoni</t>
+          <t>Sainte Beuve</t>
         </is>
       </c>
       <c r="B161">
-        <v>3.913329756986799E-05</v>
+        <v>3.868028743684522E-05</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Schmoller</t>
+          <t>Gotthold Ephraim Lessing</t>
         </is>
       </c>
       <c r="B162">
-        <v>3.905603922681392E-05</v>
+        <v>3.855424356066302E-05</v>
       </c>
     </row>
     <row r="163">
@@ -2433,37 +2433,37 @@
         </is>
       </c>
       <c r="B163">
-        <v>3.904277805634073E-05</v>
+        <v>3.82080430389153E-05</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sainte Beuve</t>
+          <t>Gustav Freytag</t>
         </is>
       </c>
       <c r="B164">
-        <v>3.898402205072472E-05</v>
+        <v>3.805572799147339E-05</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Gustav Freytag</t>
+          <t>Richard Cobden</t>
         </is>
       </c>
       <c r="B165">
-        <v>3.887162625194815E-05</v>
+        <v>3.779986076909894E-05</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Richard Cobden</t>
+          <t>Eduard von Hartmann</t>
         </is>
       </c>
       <c r="B166">
-        <v>3.882606440282613E-05</v>
+        <v>3.774292780649921E-05</v>
       </c>
     </row>
     <row r="167">
@@ -2473,17 +2473,17 @@
         </is>
       </c>
       <c r="B167">
-        <v>3.874497205547812E-05</v>
+        <v>3.770129384732229E-05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Eduard von Hartmann</t>
+          <t>Otto Pfleiderer</t>
         </is>
       </c>
       <c r="B168">
-        <v>3.857328100484294E-05</v>
+        <v>3.763210280552671E-05</v>
       </c>
     </row>
     <row r="169">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B169">
-        <v>3.842052085579196E-05</v>
+        <v>3.759542113276965E-05</v>
       </c>
     </row>
     <row r="170">
@@ -2503,27 +2503,27 @@
         </is>
       </c>
       <c r="B170">
-        <v>3.822083634233357E-05</v>
+        <v>3.738927748148203E-05</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Theodor Fontane</t>
+          <t>Külpe</t>
         </is>
       </c>
       <c r="B171">
-        <v>3.82081659833946E-05</v>
+        <v>3.736401423935413E-05</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Külpe</t>
+          <t>Theodor Fontane</t>
         </is>
       </c>
       <c r="B172">
-        <v>3.820803552443326E-05</v>
+        <v>3.73593795941199E-05</v>
       </c>
     </row>
     <row r="173">
@@ -2533,67 +2533,67 @@
         </is>
       </c>
       <c r="B173">
-        <v>3.820538749049085E-05</v>
+        <v>3.734562421594463E-05</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Otto Pfleiderer</t>
+          <t>Eduard Zeller</t>
         </is>
       </c>
       <c r="B174">
-        <v>3.811614510763999E-05</v>
+        <v>3.721053793657262E-05</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Eduard Zeller</t>
+          <t>Friedrich Carl von Savigny</t>
         </is>
       </c>
       <c r="B175">
-        <v>3.806028048101597E-05</v>
+        <v>3.720939940464238E-05</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Friedrich Carl von Savigny</t>
+          <t>Hermann Lotze</t>
         </is>
       </c>
       <c r="B176">
-        <v>3.805151613261041E-05</v>
+        <v>3.709213707596561E-05</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Hermann Lotze</t>
+          <t>Ludwig Büchner</t>
         </is>
       </c>
       <c r="B177">
-        <v>3.794504414176514E-05</v>
+        <v>3.700411638836883E-05</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ludwig Büchner</t>
+          <t>Franz Brentano</t>
         </is>
       </c>
       <c r="B178">
-        <v>3.785638321982265E-05</v>
+        <v>3.674030980711497E-05</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Franz Brentano</t>
+          <t>Schmoller</t>
         </is>
       </c>
       <c r="B179">
-        <v>3.762390579677276E-05</v>
+        <v>3.665918656979258E-05</v>
       </c>
     </row>
     <row r="180">
@@ -2603,67 +2603,67 @@
         </is>
       </c>
       <c r="B180">
-        <v>3.695496568745579E-05</v>
+        <v>3.604633926544985E-05</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Karl Mannheim</t>
+          <t>Norbert Elias</t>
         </is>
       </c>
       <c r="B181">
-        <v>3.688109872835584E-05</v>
+        <v>3.568495054820612E-05</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Norbert Elias</t>
+          <t>Carl Stumpf</t>
         </is>
       </c>
       <c r="B182">
-        <v>3.660426887409959E-05</v>
+        <v>3.567136330804809E-05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Carl Stumpf</t>
+          <t>Friedrich Heinrich Jacobi</t>
         </is>
       </c>
       <c r="B183">
-        <v>3.659747905343043E-05</v>
+        <v>3.556623168271304E-05</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Friedrich Heinrich Jacobi</t>
+          <t>Bernard Bolzano</t>
         </is>
       </c>
       <c r="B184">
-        <v>3.649301165012917E-05</v>
+        <v>3.537313932375333E-05</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Bernard Bolzano</t>
+          <t>Charles Fourier</t>
         </is>
       </c>
       <c r="B185">
-        <v>3.630963330286127E-05</v>
+        <v>3.452806365881671E-05</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Charles Fourier</t>
+          <t>Karl Mannheim</t>
         </is>
       </c>
       <c r="B186">
-        <v>3.519113230001485E-05</v>
+        <v>3.445464705191679E-05</v>
       </c>
     </row>
     <row r="187">
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="B187">
-        <v>3.244002259715569E-05</v>
+        <v>3.278700677995993E-05</v>
       </c>
     </row>
     <row r="188">
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="B188">
-        <v>3.163010539733528E-05</v>
+        <v>3.103123389660141E-05</v>
       </c>
     </row>
     <row r="189">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="B189">
-        <v>3.161897175464856E-05</v>
+        <v>3.097313213996897E-05</v>
       </c>
     </row>
     <row r="190">
@@ -2703,17 +2703,17 @@
         </is>
       </c>
       <c r="B190">
-        <v>3.054206693491525E-05</v>
+        <v>2.997289128776127E-05</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Rodbertus</t>
+          <t>de Gouges</t>
         </is>
       </c>
       <c r="B191">
-        <v>3.024928283417356E-05</v>
+        <v>2.937463245941251E-05</v>
       </c>
     </row>
     <row r="192">
@@ -2723,197 +2723,197 @@
         </is>
       </c>
       <c r="B192">
-        <v>3.010604685976913E-05</v>
+        <v>2.845225899122325E-05</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>de Gouges</t>
+          <t>Rodbertus</t>
         </is>
       </c>
       <c r="B193">
-        <v>2.982725923967314E-05</v>
+        <v>2.783376472390616E-05</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Wilhelm von Humboldt</t>
+          <t>James Fitzjames Stephen</t>
         </is>
       </c>
       <c r="B194">
-        <v>2.955876397835592E-05</v>
+        <v>2.745635056624289E-05</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>James Fitzjames Stephen</t>
+          <t>Wilhelm von Humboldt</t>
         </is>
       </c>
       <c r="B195">
-        <v>2.782591532740631E-05</v>
+        <v>2.715203941789183E-05</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Leo Strauss</t>
+          <t>Plato</t>
         </is>
       </c>
       <c r="B196">
-        <v>2.673082625506073E-05</v>
+        <v>2.64183758879959E-05</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Plato</t>
+          <t>Leo Strauss</t>
         </is>
       </c>
       <c r="B197">
-        <v>2.652064954476247E-05</v>
+        <v>2.51320132606781E-05</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Eduard Bernstein</t>
+          <t>Auberon Herbert</t>
         </is>
       </c>
       <c r="B198">
-        <v>2.544229151333935E-05</v>
+        <v>2.506341198583895E-05</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Friedrich List</t>
+          <t>Lujo Brentano</t>
         </is>
       </c>
       <c r="B199">
-        <v>2.542419416364115E-05</v>
+        <v>2.505926912322658E-05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ferdinand Lassalle</t>
+          <t>Vilfredo Pareto</t>
         </is>
       </c>
       <c r="B200">
-        <v>2.531965944887088E-05</v>
+        <v>2.498938353039133E-05</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Auberon Herbert</t>
+          <t>John C Calhoun</t>
         </is>
       </c>
       <c r="B201">
-        <v>2.52784674145588E-05</v>
+        <v>2.482808008699542E-05</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Lujo Brentano</t>
+          <t>Eduard Bernstein</t>
         </is>
       </c>
       <c r="B202">
-        <v>2.527005234779125E-05</v>
+        <v>2.304645438636084E-05</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Vilfredo Pareto</t>
+          <t>Friedrich List</t>
         </is>
       </c>
       <c r="B203">
-        <v>2.514083218440544E-05</v>
+        <v>2.302904112265982E-05</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>John C Calhoun</t>
+          <t>Ferdinand Lassalle</t>
         </is>
       </c>
       <c r="B204">
-        <v>2.501647674317595E-05</v>
+        <v>2.292823367535272E-05</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>August Bebel</t>
+          <t>Gaetano Mosca</t>
         </is>
       </c>
       <c r="B205">
-        <v>2.336339282609724E-05</v>
+        <v>2.291986702289459E-05</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Gaetano Mosca</t>
+          <t>John Rawls</t>
         </is>
       </c>
       <c r="B206">
-        <v>2.299827281793383E-05</v>
+        <v>2.251624384143744E-05</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>John Rawls</t>
+          <t>Robert Nozick</t>
         </is>
       </c>
       <c r="B207">
-        <v>2.258583552851832E-05</v>
+        <v>2.162362782928951E-05</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Robert Nozick</t>
+          <t>Quentin Skinner</t>
         </is>
       </c>
       <c r="B208">
-        <v>2.163348964767049E-05</v>
+        <v>2.145388573948348E-05</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Quentin Skinner</t>
+          <t>August Bebel</t>
         </is>
       </c>
       <c r="B209">
-        <v>2.145314477928316E-05</v>
+        <v>2.098052048934598E-05</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Schäffle</t>
+          <t>Aristotle</t>
         </is>
       </c>
       <c r="B210">
-        <v>2.064941645628456E-05</v>
+        <v>2.041017755253559E-05</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Aristotle</t>
+          <t>Schäffle</t>
         </is>
       </c>
       <c r="B211">
-        <v>2.050986979376631E-05</v>
+        <v>1.829036454897614E-05</v>
       </c>
     </row>
     <row r="212">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="B212">
-        <v>1.85401033944581E-05</v>
+        <v>1.618570222196208E-05</v>
       </c>
     </row>
     <row r="213">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="B213">
-        <v>1.829498488743105E-06</v>
+        <v>1.831454376797223E-06</v>
       </c>
     </row>
   </sheetData>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.000122078276005299</v>
+        <v>0.0001306899594580099</v>
       </c>
     </row>
     <row r="3">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.001677954950104905</v>
+        <v>0.00199818845125424</v>
       </c>
     </row>
     <row r="18">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.0003676133038546824</v>
+        <v>0.0007974015895149021</v>
       </c>
     </row>
     <row r="33">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.01207341321895301</v>
+        <v>0.01239200624077135</v>
       </c>
     </row>
     <row r="48">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.005123921971682962</v>
+        <v>0.0035656014024769</v>
       </c>
     </row>
     <row r="63">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>0.000712825475164603</v>
+        <v>1.675594695933282E-05</v>
       </c>
     </row>
     <row r="78">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.0002464608338230988</v>
+        <v>1.860476336612014E-05</v>
       </c>
     </row>
     <row r="93">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="B107">
-        <v>0.001655228288332932</v>
+        <v>0.00164371165640457</v>
       </c>
     </row>
     <row r="108">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="B122">
-        <v>0.00174839142369411</v>
+        <v>0.001760866665384632</v>
       </c>
     </row>
     <row r="123">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.0009901750804115952</v>
+        <v>0.001012341322882629</v>
       </c>
     </row>
     <row r="138">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="B152">
-        <v>0.01454809198045166</v>
+        <v>0.01404072279448848</v>
       </c>
     </row>
     <row r="153">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="B167">
-        <v>0.3075256362128195</v>
+        <v>0.3076235428241138</v>
       </c>
     </row>
     <row r="168">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="B182">
-        <v>0.3790000520780247</v>
+        <v>0.3790755525720869</v>
       </c>
     </row>
     <row r="183">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="B197">
-        <v>0.2742081569066769</v>
+        <v>0.275924013810838</v>
       </c>
     </row>
   </sheetData>
@@ -4955,7 +4955,7 @@
         <v>0.9828230022404779</v>
       </c>
       <c r="C2">
-        <v>0.9792625052213076</v>
+        <v>0.9792546366443701</v>
       </c>
     </row>
     <row r="3">
@@ -4968,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.005310730195523122</v>
+        <v>0.005225657165861065</v>
       </c>
     </row>
     <row r="4">
@@ -4981,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.9883365565619291</v>
+        <v>0.9894785680699258</v>
       </c>
     </row>
     <row r="5">
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.001746332258851072</v>
+        <v>0.001725397773382168</v>
       </c>
     </row>
     <row r="6">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.001138337829834593</v>
+        <v>0.00114924857618599</v>
       </c>
     </row>
     <row r="7">
@@ -5020,7 +5020,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.001004010029470013</v>
+        <v>0.001005446679584323</v>
       </c>
     </row>
     <row r="8">
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.002330459958186811</v>
+        <v>0.00128006300256135</v>
       </c>
     </row>
     <row r="9">
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.0001278457671631704</v>
+        <v>0.0001271867545352538</v>
       </c>
     </row>
     <row r="10">
@@ -5059,7 +5059,7 @@
         <v>0.9381107491856677</v>
       </c>
       <c r="C10">
-        <v>0.9381013800760789</v>
+        <v>0.938101721652439</v>
       </c>
     </row>
     <row r="11">
@@ -5072,7 +5072,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.9876132454393443</v>
+        <v>0.9877507500090036</v>
       </c>
     </row>
     <row r="12">
@@ -5085,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.993045675765402</v>
+        <v>0.9930725458885264</v>
       </c>
     </row>
     <row r="13">
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.0009063926940639269</v>
+        <v>0.0009079534758289312</v>
       </c>
       <c r="C13">
-        <v>0.000902447966316892</v>
+        <v>0.0009041837741208693</v>
       </c>
     </row>
     <row r="14">
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.0007442922374429223</v>
+        <v>0.000745175166536602</v>
       </c>
       <c r="C14">
-        <v>0.0007255864947602847</v>
+        <v>0.000726783734896959</v>
       </c>
     </row>
     <row r="15">
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.0007570776255707762</v>
+        <v>0.0007594701653424955</v>
       </c>
       <c r="C15">
-        <v>0.0008094316274286017</v>
+        <v>0.0008109109359950554</v>
       </c>
     </row>
   </sheetData>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.413409818123165</v>
+        <v>1.413562237633913</v>
       </c>
     </row>
     <row r="3">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3786407766990291</v>
+        <v>0.4086538461538461</v>
       </c>
     </row>
     <row r="4">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>11.61697366284462</v>
+        <v>10.72994956836261</v>
       </c>
     </row>
     <row r="3">
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>8.552597094559736</v>
+        <v>8.228544497307308</v>
       </c>
     </row>
     <row r="4">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>8.053005827936399</v>
+        <v>6.886618957038423</v>
       </c>
     </row>
     <row r="5">
@@ -5238,7 +5238,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>6.818682074624866</v>
+        <v>6.708109499015392</v>
       </c>
     </row>
     <row r="6">
@@ -5248,17 +5248,17 @@
         </is>
       </c>
       <c r="B6">
-        <v>5.389082522138355</v>
+        <v>5.263445662012006</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>August Bebel</t>
+          <t>Frederick Douglass</t>
         </is>
       </c>
       <c r="B7">
-        <v>4.756293789700844</v>
+        <v>5.252365035387405</v>
       </c>
     </row>
     <row r="8">
@@ -5268,187 +5268,187 @@
         </is>
       </c>
       <c r="B8">
-        <v>4.743244308613038</v>
+        <v>4.988469885401648</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Robert Merton</t>
+          <t>Scheler</t>
         </is>
       </c>
       <c r="B9">
-        <v>4.712086704489674</v>
+        <v>4.639563016280596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scheler</t>
+          <t>Montaigne</t>
         </is>
       </c>
       <c r="B10">
-        <v>4.662364432547999</v>
+        <v>3.922602166581441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Montaigne</t>
+          <t>Robert Merton</t>
         </is>
       </c>
       <c r="B11">
-        <v>3.930061180932157</v>
+        <v>3.675433304765021</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karl Jaspers</t>
+          <t>Leo Strauss</t>
         </is>
       </c>
       <c r="B12">
-        <v>3.42964081166001</v>
+        <v>3.563270953196257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Windelband</t>
+          <t>Herbert Spencer</t>
         </is>
       </c>
       <c r="B13">
-        <v>3.300414461839874</v>
+        <v>3.561244565791572</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Grimmelshausen</t>
+          <t>Karl Jaspers</t>
         </is>
       </c>
       <c r="B14">
-        <v>3.09354255700876</v>
+        <v>3.420369947981517</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>John Milton</t>
+          <t>August Bebel</t>
         </is>
       </c>
       <c r="B15">
-        <v>3.027214303459847</v>
+        <v>3.342439180689259</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Talcott Parsons</t>
+          <t>Joseph Lister</t>
         </is>
       </c>
       <c r="B16">
-        <v>3.008378190206333</v>
+        <v>3.274284051389019</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Herbert Spencer</t>
+          <t>Talcott Parsons</t>
         </is>
       </c>
       <c r="B17">
-        <v>2.974057800843173</v>
+        <v>3.107845300070866</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karl Mannheim</t>
+          <t>Grimmelshausen</t>
         </is>
       </c>
       <c r="B18">
-        <v>2.91761265233121</v>
+        <v>3.036483865959108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Frege</t>
+          <t>Durkheim</t>
         </is>
       </c>
       <c r="B19">
-        <v>2.826260071985881</v>
+        <v>3.001350220088252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Voltaire</t>
+          <t>Philip Nichols</t>
         </is>
       </c>
       <c r="B20">
-        <v>2.77506974749421</v>
+        <v>2.999720477677419</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Durkheim</t>
+          <t>Karl Mannheim</t>
         </is>
       </c>
       <c r="B21">
-        <v>2.773845450858864</v>
+        <v>2.945421918255511</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jean Racine</t>
+          <t>Windelband</t>
         </is>
       </c>
       <c r="B22">
-        <v>2.706929728717003</v>
+        <v>2.943860248480263</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>William Wordsworth</t>
+          <t>Frege</t>
         </is>
       </c>
       <c r="B23">
-        <v>2.665400078875907</v>
+        <v>2.838624285674011</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Leo Strauss</t>
+          <t>John Milton</t>
         </is>
       </c>
       <c r="B24">
-        <v>2.660674508272354</v>
+        <v>2.753536789978107</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rousseau</t>
+          <t>Jean Racine</t>
         </is>
       </c>
       <c r="B25">
-        <v>2.602427353930625</v>
+        <v>2.649674690058914</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Thünen</t>
+          <t>Rousseau</t>
         </is>
       </c>
       <c r="B26">
-        <v>2.587372731293056</v>
+        <v>2.630154814519086</v>
       </c>
     </row>
     <row r="27">
@@ -5458,77 +5458,77 @@
         </is>
       </c>
       <c r="B27">
-        <v>2.563968125188696</v>
+        <v>2.577005275304558</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Richard Cobden</t>
+          <t>Thünen</t>
         </is>
       </c>
       <c r="B28">
-        <v>2.546417378223436</v>
+        <v>2.572236541643446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gotthold Ephraim Lessing</t>
+          <t>Kempis</t>
         </is>
       </c>
       <c r="B29">
-        <v>2.511688548106871</v>
+        <v>2.493616192215562</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Oswald Spengler</t>
+          <t>Wilhelm von Humboldt</t>
         </is>
       </c>
       <c r="B30">
-        <v>2.465941222725916</v>
+        <v>2.474094352887405</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vilfredo Pareto</t>
+          <t>Oswald Spengler</t>
         </is>
       </c>
       <c r="B31">
-        <v>2.419229618212691</v>
+        <v>2.453646996385221</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Joseph Lister</t>
+          <t>Vilfredo Pareto</t>
         </is>
       </c>
       <c r="B32">
-        <v>2.379634898101184</v>
+        <v>2.41563238079798</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wilhelm von Humboldt</t>
+          <t>Thomas Browne</t>
         </is>
       </c>
       <c r="B33">
-        <v>2.36940339288202</v>
+        <v>2.408619715233602</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Thomas Browne</t>
+          <t>Ambroise Paré</t>
         </is>
       </c>
       <c r="B34">
-        <v>2.340708442521917</v>
+        <v>2.344638271452018</v>
       </c>
     </row>
     <row r="35">
@@ -5538,277 +5538,277 @@
         </is>
       </c>
       <c r="B35">
-        <v>2.313213017978242</v>
+        <v>2.338343412378741</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kempis</t>
+          <t>Voltaire</t>
         </is>
       </c>
       <c r="B36">
-        <v>2.262842340653669</v>
+        <v>2.320754460371891</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>John Stuart Mill</t>
+          <t>Pierre Corneille</t>
         </is>
       </c>
       <c r="B37">
-        <v>2.256678095821664</v>
+        <v>2.287632363764892</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Franz Brentano</t>
+          <t>Francis Bacon</t>
         </is>
       </c>
       <c r="B38">
-        <v>2.252914985867833</v>
+        <v>2.245208490957072</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Clausewitz</t>
+          <t>Copernicus</t>
         </is>
       </c>
       <c r="B39">
-        <v>2.245814564591449</v>
+        <v>2.182401915854543</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Faraday</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="B40">
-        <v>2.226014050256451</v>
+        <v>2.105185610579823</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Malory</t>
+          <t>Edward Bellamy</t>
         </is>
       </c>
       <c r="B41">
-        <v>2.218930666388215</v>
+        <v>2.02797803234559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pierre Corneille</t>
+          <t>Clausewitz</t>
         </is>
       </c>
       <c r="B42">
-        <v>2.218877915529838</v>
+        <v>1.996813980907075</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Copernicus</t>
+          <t>Ernst Cassirer</t>
         </is>
       </c>
       <c r="B43">
-        <v>2.163176102878214</v>
+        <v>1.995340195289699</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Isaiah Berlin</t>
         </is>
       </c>
       <c r="B44">
-        <v>2.155982715219074</v>
+        <v>1.962471402936975</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Francis Bacon</t>
+          <t>Malory</t>
         </is>
       </c>
       <c r="B45">
-        <v>2.152113117965072</v>
+        <v>1.958865838708391</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ambroise Paré</t>
+          <t>Richard Cobden</t>
         </is>
       </c>
       <c r="B46">
-        <v>2.129115199349011</v>
+        <v>1.958259060348511</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Edward Bellamy</t>
+          <t>John Stuart Mill</t>
         </is>
       </c>
       <c r="B47">
-        <v>2.018978803875795</v>
+        <v>1.921134948024344</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Plutarch</t>
+          <t>Franz Brentano</t>
         </is>
       </c>
       <c r="B48">
-        <v>1.999392799206908</v>
+        <v>1.917149448066162</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Froissart</t>
+          <t>William Graham Sumner</t>
         </is>
       </c>
       <c r="B49">
-        <v>1.985119999869743</v>
+        <v>1.882594902527254</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Oscar Wilde</t>
+          <t>Ebbinghaus</t>
         </is>
       </c>
       <c r="B50">
-        <v>1.870903857993355</v>
+        <v>1.878194229342244</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>William Graham Sumner</t>
+          <t>Plutarch</t>
         </is>
       </c>
       <c r="B51">
-        <v>1.85944182449802</v>
+        <v>1.852071152652844</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hume</t>
+          <t>Otto Pfleiderer</t>
         </is>
       </c>
       <c r="B52">
-        <v>1.784917197301955</v>
+        <v>1.835050941297021</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kropotkin</t>
+          <t>Euripides</t>
         </is>
       </c>
       <c r="B53">
-        <v>1.764683620497264</v>
+        <v>1.810782169096777</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>de Gouges</t>
+          <t>Kropotkin</t>
         </is>
       </c>
       <c r="B54">
-        <v>1.761027944241773</v>
+        <v>1.758645049534417</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ebbinghaus</t>
+          <t>Hermann Lotze</t>
         </is>
       </c>
       <c r="B55">
-        <v>1.74503342533126</v>
+        <v>1.713645817058777</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hermann Lotze</t>
+          <t>Schmoller</t>
         </is>
       </c>
       <c r="B56">
-        <v>1.720162218568678</v>
+        <v>1.705636268537664</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Schmoller</t>
+          <t>Jonathan Swift</t>
         </is>
       </c>
       <c r="B57">
-        <v>1.694300856031493</v>
+        <v>1.691070471672246</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ernst Cassirer</t>
+          <t>Robert Nozick</t>
         </is>
       </c>
       <c r="B58">
-        <v>1.689187860474947</v>
+        <v>1.65383754386563</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cervantes</t>
+          <t>Simon Newcomb</t>
         </is>
       </c>
       <c r="B59">
-        <v>1.689079370694853</v>
+        <v>1.628466285625251</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Robert Nozick</t>
+          <t>Samuel Johnson</t>
         </is>
       </c>
       <c r="B60">
-        <v>1.659963617263742</v>
+        <v>1.612838923499801</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Euripides</t>
+          <t>Bastiat</t>
         </is>
       </c>
       <c r="B61">
-        <v>1.618568082244545</v>
+        <v>1.612192294150609</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>James Fitzjames Stephen</t>
+          <t>Hume</t>
         </is>
       </c>
       <c r="B62">
-        <v>1.602264784294922</v>
+        <v>1.592953220801066</v>
       </c>
     </row>
     <row r="63">
@@ -5818,77 +5818,77 @@
         </is>
       </c>
       <c r="B63">
-        <v>1.58724478201719</v>
+        <v>1.584516169397028</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Oliver Goldsmith</t>
+          <t>Spinoza</t>
         </is>
       </c>
       <c r="B64">
-        <v>1.566428191086804</v>
+        <v>1.582774246334916</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Bastiat</t>
+          <t>Oliver Goldsmith</t>
         </is>
       </c>
       <c r="B65">
-        <v>1.557504505256737</v>
+        <v>1.572639319611447</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tocqueville</t>
+          <t>Ernst Jünger</t>
         </is>
       </c>
       <c r="B66">
-        <v>1.555999203659868</v>
+        <v>1.552180035577003</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jonathan Swift</t>
+          <t>Lujo Brentano</t>
         </is>
       </c>
       <c r="B67">
-        <v>1.554929849143194</v>
+        <v>1.536534265571054</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ernst Jünger</t>
+          <t>Tocqueville</t>
         </is>
       </c>
       <c r="B68">
-        <v>1.554702477142119</v>
+        <v>1.534116403340894</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Lujo Brentano</t>
+          <t>Hölderlin</t>
         </is>
       </c>
       <c r="B69">
-        <v>1.553373667454781</v>
+        <v>1.521683818516188</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hölderlin</t>
+          <t>William Wordsworth</t>
         </is>
       </c>
       <c r="B70">
-        <v>1.525107939817755</v>
+        <v>1.512566372404171</v>
       </c>
     </row>
     <row r="71">
@@ -5898,17 +5898,17 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.518301500792619</v>
+        <v>1.509355678610898</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>John Calvin</t>
+          <t>Sainte Beuve</t>
         </is>
       </c>
       <c r="B72">
-        <v>1.499894541601829</v>
+        <v>1.507938701257036</v>
       </c>
     </row>
     <row r="73">
@@ -5918,87 +5918,87 @@
         </is>
       </c>
       <c r="B73">
-        <v>1.483677951071765</v>
+        <v>1.507461680723003</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Samuel Johnson</t>
+          <t>John Calvin</t>
         </is>
       </c>
       <c r="B74">
-        <v>1.462792549112742</v>
+        <v>1.502807884106996</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gaetano Mosca</t>
+          <t>Oscar Wilde</t>
         </is>
       </c>
       <c r="B75">
-        <v>1.457183784882911</v>
+        <v>1.484901512256507</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>William Caxton</t>
+          <t>Benjamin Constant</t>
         </is>
       </c>
       <c r="B76">
-        <v>1.437443412376018</v>
+        <v>1.480404284793935</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Edgar Jung</t>
+          <t>Gotthold Ephraim Lessing</t>
         </is>
       </c>
       <c r="B77">
-        <v>1.43346190435018</v>
+        <v>1.468500471578757</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Descartes</t>
+          <t>Theodor Fontane</t>
         </is>
       </c>
       <c r="B78">
-        <v>1.420134925494939</v>
+        <v>1.468150317985802</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Carl Schmitt</t>
+          <t>Friedrich List</t>
         </is>
       </c>
       <c r="B79">
-        <v>1.413409818123165</v>
+        <v>1.453490072628103</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Thoreau</t>
+          <t>Gaetano Mosca</t>
         </is>
       </c>
       <c r="B80">
-        <v>1.40823245650865</v>
+        <v>1.439049543095794</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>John C Calhoun</t>
+          <t>Edgar Jung</t>
         </is>
       </c>
       <c r="B81">
-        <v>1.397053886751412</v>
+        <v>1.432164002665926</v>
       </c>
     </row>
     <row r="82">
@@ -6008,237 +6008,237 @@
         </is>
       </c>
       <c r="B82">
-        <v>1.39370480510537</v>
+        <v>1.423976551602303</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Herder</t>
+          <t>Epictetus</t>
         </is>
       </c>
       <c r="B83">
-        <v>1.363258989541241</v>
+        <v>1.419066855840941</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Thomas Mann</t>
+          <t>Descartes</t>
         </is>
       </c>
       <c r="B84">
-        <v>1.362674879695034</v>
+        <v>1.416434714809117</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Friedrich Carl von Savigny</t>
+          <t>John C Calhoun</t>
         </is>
       </c>
       <c r="B85">
-        <v>1.33258199028398</v>
+        <v>1.416420283211163</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Theodor Fontane</t>
+          <t>Carl Schmitt</t>
         </is>
       </c>
       <c r="B86">
-        <v>1.316777135285076</v>
+        <v>1.413562237633913</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cicero</t>
+          <t>Herder</t>
         </is>
       </c>
       <c r="B87">
-        <v>1.309779041885122</v>
+        <v>1.386821565248844</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Herbart</t>
+          <t>William Caxton</t>
         </is>
       </c>
       <c r="B88">
-        <v>1.3057996587392</v>
+        <v>1.384730576897199</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hippolyte Taine</t>
+          <t>Henry George</t>
         </is>
       </c>
       <c r="B89">
-        <v>1.30550263562613</v>
+        <v>1.3799918422535</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>James Fitzjames Stephen</t>
         </is>
       </c>
       <c r="B90">
-        <v>1.304321461563599</v>
+        <v>1.378186106451485</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ralph Waldo Emerson</t>
+          <t>Thoreau</t>
         </is>
       </c>
       <c r="B91">
-        <v>1.295516800809381</v>
+        <v>1.372004097820649</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Friedrich Schiller</t>
+          <t>Cervantes</t>
         </is>
       </c>
       <c r="B92">
-        <v>1.293335083446061</v>
+        <v>1.371416927682027</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Hippocrates</t>
+          <t>Bernard Bolzano</t>
         </is>
       </c>
       <c r="B93">
-        <v>1.267837476695903</v>
+        <v>1.3650318122097</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gustav Freytag</t>
+          <t>Faraday</t>
         </is>
       </c>
       <c r="B94">
-        <v>1.265924837611795</v>
+        <v>1.358826865189302</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sainte Beuve</t>
+          <t>Ralph Waldo Emerson</t>
         </is>
       </c>
       <c r="B95">
-        <v>1.257002466762431</v>
+        <v>1.357445849752845</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bentham</t>
+          <t>Walter Raleigh</t>
         </is>
       </c>
       <c r="B96">
-        <v>1.251527713067156</v>
+        <v>1.31209779036555</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pliny the Younger</t>
+          <t>Herbart</t>
         </is>
       </c>
       <c r="B97">
-        <v>1.23334472780553</v>
+        <v>1.312041226565313</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sombart</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="B98">
-        <v>1.223329338939667</v>
+        <v>1.30421066478182</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Raymond Aron</t>
+          <t>Nassau Senior</t>
         </is>
       </c>
       <c r="B99">
-        <v>1.22314393947265</v>
+        <v>1.302702391915217</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Edward Jenner</t>
+          <t>Cicero</t>
         </is>
       </c>
       <c r="B100">
-        <v>1.221432129949578</v>
+        <v>1.300374774742531</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Hans Kelsen</t>
+          <t>Friedrich Carl von Savigny</t>
         </is>
       </c>
       <c r="B101">
-        <v>1.220913268103439</v>
+        <v>1.28471925531442</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>John Ruskin</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B102">
-        <v>1.220473686941044</v>
+        <v>1.27642499178527</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Adam Smith</t>
+          <t>Thomas Mann</t>
         </is>
       </c>
       <c r="B103">
-        <v>1.22047164924052</v>
+        <v>1.263972854802012</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Gustav Freytag</t>
         </is>
       </c>
       <c r="B104">
-        <v>1.215606565428926</v>
+        <v>1.262375660516375</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Edmund Burke</t>
+          <t>Hippocrates</t>
         </is>
       </c>
       <c r="B105">
-        <v>1.210643880054005</v>
+        <v>1.259492713531223</v>
       </c>
     </row>
     <row r="106">
@@ -6248,787 +6248,787 @@
         </is>
       </c>
       <c r="B106">
-        <v>1.209291482765297</v>
+        <v>1.251907623309109</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Homer</t>
+          <t>Sombart</t>
         </is>
       </c>
       <c r="B107">
-        <v>1.200413820727177</v>
+        <v>1.251846757153466</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Malthus</t>
+          <t>Bentham</t>
         </is>
       </c>
       <c r="B108">
-        <v>1.198642925155868</v>
+        <v>1.247829514181602</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Victor Hugo</t>
+          <t>Adam Smith</t>
         </is>
       </c>
       <c r="B109">
-        <v>1.194102924538273</v>
+        <v>1.243851716964812</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>William Harvey</t>
+          <t>William Roper</t>
         </is>
       </c>
       <c r="B110">
-        <v>1.189695349398989</v>
+        <v>1.237036181279368</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Schleiermacher</t>
+          <t>Edward Jenner</t>
         </is>
       </c>
       <c r="B111">
-        <v>1.181156352916738</v>
+        <v>1.232316220786952</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Isaiah Berlin</t>
+          <t>Froissart</t>
         </is>
       </c>
       <c r="B112">
-        <v>1.181107539463006</v>
+        <v>1.225620453763393</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Raymond Aron</t>
         </is>
       </c>
       <c r="B113">
-        <v>1.178291102301933</v>
+        <v>1.225036010339473</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Spinoza</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="B114">
-        <v>1.174970229534923</v>
+        <v>1.212464554254535</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Philip Nichols</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B115">
-        <v>1.174373940133539</v>
+        <v>1.206389166590079</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>William Godwin</t>
+          <t>Malthus</t>
         </is>
       </c>
       <c r="B116">
-        <v>1.164063341027425</v>
+        <v>1.205911177549022</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>William Harrison</t>
+          <t>Friedrich Schiller</t>
         </is>
       </c>
       <c r="B117">
-        <v>1.158981965365035</v>
+        <v>1.205737253941651</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Molière</t>
+          <t>John Ruskin</t>
         </is>
       </c>
       <c r="B118">
-        <v>1.152093781068352</v>
+        <v>1.199100659821376</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Edward Haies</t>
+          <t>Edmund Burke</t>
         </is>
       </c>
       <c r="B119">
-        <v>1.149061818197234</v>
+        <v>1.196869296090442</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Eduard Bernstein</t>
+          <t>Victor Hugo</t>
         </is>
       </c>
       <c r="B120">
-        <v>1.143374138689514</v>
+        <v>1.191278946561566</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Schäffle</t>
+          <t>Külpe</t>
         </is>
       </c>
       <c r="B121">
-        <v>1.138300205652922</v>
+        <v>1.181833152578916</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Aristophanes</t>
         </is>
       </c>
       <c r="B122">
-        <v>1.137390485954472</v>
+        <v>1.1749170895434</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Marcus Aurelius</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="B123">
-        <v>1.12862224008775</v>
+        <v>1.169873061126426</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Hermann Cohen</t>
+          <t>Schleiermacher</t>
         </is>
       </c>
       <c r="B124">
-        <v>1.122538797981547</v>
+        <v>1.165109931048998</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Rilke</t>
+          <t>Molière</t>
         </is>
       </c>
       <c r="B125">
-        <v>1.118494625157428</v>
+        <v>1.145572061785247</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>William Roper</t>
+          <t>William Godwin</t>
         </is>
       </c>
       <c r="B126">
-        <v>1.116981174675057</v>
+        <v>1.139575527375535</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Walter Raleigh</t>
+          <t>Edward Haies</t>
         </is>
       </c>
       <c r="B127">
-        <v>1.112788151660075</v>
+        <v>1.139144353254463</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Simon Newcomb</t>
+          <t>Hermann Cohen</t>
         </is>
       </c>
       <c r="B128">
-        <v>1.112696058874781</v>
+        <v>1.131039658832967</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Renan</t>
+          <t>Rilke</t>
         </is>
       </c>
       <c r="B129">
-        <v>1.096887189573122</v>
+        <v>1.120239620561303</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Max Weber</t>
+          <t>Hippolyte Taine</t>
         </is>
       </c>
       <c r="B130">
-        <v>1.085350796383641</v>
+        <v>1.106592529469129</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Carl Friedrich</t>
+          <t>Pedro Calderón de la Barca</t>
         </is>
       </c>
       <c r="B131">
-        <v>1.073255424259087</v>
+        <v>1.091424059990733</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Thucydides</t>
+          <t>Max Weber</t>
         </is>
       </c>
       <c r="B132">
-        <v>1.072249840455574</v>
+        <v>1.083994520512595</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>E T A Hoffmann</t>
+          <t>Robert Browning</t>
         </is>
       </c>
       <c r="B133">
-        <v>1.071486704703416</v>
+        <v>1.075867382673796</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Newton</t>
+          <t>E T A Hoffmann</t>
         </is>
       </c>
       <c r="B134">
-        <v>1.066362768141513</v>
+        <v>1.071426397524377</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Otto Pfleiderer</t>
+          <t>Newton</t>
         </is>
       </c>
       <c r="B135">
-        <v>1.056767230001096</v>
+        <v>1.06705807716942</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Archibald Geikie</t>
+          <t>Marcus Aurelius</t>
         </is>
       </c>
       <c r="B136">
-        <v>1.052206477920823</v>
+        <v>1.065920943165869</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Virgil</t>
+          <t>Schäffle</t>
         </is>
       </c>
       <c r="B137">
-        <v>1.030230202328124</v>
+        <v>1.063553274724834</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Izaak Walton</t>
+          <t>Thucydides</t>
         </is>
       </c>
       <c r="B138">
-        <v>1.028879155432961</v>
+        <v>1.061365611403594</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>John Woolman</t>
+          <t>Archibald Geikie</t>
         </is>
       </c>
       <c r="B139">
-        <v>1.027161886364184</v>
+        <v>1.054832845658433</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Epictetus</t>
+          <t>Alessandro Manzoni</t>
         </is>
       </c>
       <c r="B140">
-        <v>1.020933068419078</v>
+        <v>1.051714402366658</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Leibniz</t>
+          <t>Carl Stumpf</t>
         </is>
       </c>
       <c r="B141">
-        <v>1.005329734899685</v>
+        <v>1.044207670393725</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>John Bunyan</t>
+          <t>Leibniz</t>
         </is>
       </c>
       <c r="B142">
-        <v>1.003875249442759</v>
+        <v>1.030630226288451</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Barthold Georg Niebuhr</t>
+          <t>Pericles</t>
         </is>
       </c>
       <c r="B143">
-        <v>0.9950689582670826</v>
+        <v>1.0297884223406</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Eduard von Hartmann</t>
+          <t>John Woolman</t>
         </is>
       </c>
       <c r="B144">
-        <v>0.9778985034573038</v>
+        <v>1.027091246391586</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Alessandro Manzoni</t>
+          <t>John Bunyan</t>
         </is>
       </c>
       <c r="B145">
-        <v>0.9717190399498212</v>
+        <v>1.01040046291405</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Robert Burns</t>
+          <t>Barthold Georg Niebuhr</t>
         </is>
       </c>
       <c r="B146">
-        <v>0.9677780404135183</v>
+        <v>0.9972584704286062</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Augustine</t>
+          <t>de Gouges</t>
         </is>
       </c>
       <c r="B147">
-        <v>0.9618624265549734</v>
+        <v>0.9880066251395045</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Carl Stumpf</t>
+          <t>Eduard von Hartmann</t>
         </is>
       </c>
       <c r="B148">
-        <v>0.9608996681513142</v>
+        <v>0.9814230674833553</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Wundt</t>
+          <t>William Harvey</t>
         </is>
       </c>
       <c r="B149">
-        <v>0.9573524540889563</v>
+        <v>0.9667278038658536</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Quentin Skinner</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="B150">
-        <v>0.9463338851269254</v>
+        <v>0.9649977756077808</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sismondi</t>
+          <t>William Harrison</t>
         </is>
       </c>
       <c r="B151">
-        <v>0.9455491205113936</v>
+        <v>0.9532671092892854</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Carl Friedrich</t>
         </is>
       </c>
       <c r="B152">
-        <v>0.9397245939807627</v>
+        <v>0.9457381857562728</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Norbert Elias</t>
+          <t>Quentin Skinner</t>
         </is>
       </c>
       <c r="B153">
-        <v>0.9357591290613669</v>
+        <v>0.9437880963822626</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mazzini</t>
+          <t>Robert Burns</t>
         </is>
       </c>
       <c r="B154">
-        <v>0.9128470543250223</v>
+        <v>0.9428221322707971</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Bernard Bolzano</t>
+          <t>Sismondi</t>
         </is>
       </c>
       <c r="B155">
-        <v>0.9037117204104098</v>
+        <v>0.9378920549158241</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Lord Byron</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="B156">
-        <v>0.9031761340326547</v>
+        <v>0.9362536352128749</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>David Ricardo</t>
+          <t>Renan</t>
         </is>
       </c>
       <c r="B157">
-        <v>0.9021447268563381</v>
+        <v>0.9299983643665154</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Francis Pretty</t>
+          <t>Virgil</t>
         </is>
       </c>
       <c r="B158">
-        <v>0.9010637947740713</v>
+        <v>0.9277660730863198</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Cellini</t>
+          <t>Norbert Elias</t>
         </is>
       </c>
       <c r="B159">
-        <v>0.8999083694432327</v>
+        <v>0.9245842388239767</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ferdinand Lassalle</t>
+          <t>Mazzini</t>
         </is>
       </c>
       <c r="B160">
-        <v>0.8910497316072161</v>
+        <v>0.9170811241874895</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Nassau Senior</t>
+          <t>Lord Byron</t>
         </is>
       </c>
       <c r="B161">
-        <v>0.8880697680902941</v>
+        <v>0.9112072559494292</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Külpe</t>
+          <t>Thomas More</t>
         </is>
       </c>
       <c r="B162">
-        <v>0.8731075687074229</v>
+        <v>0.9026507203978749</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Benjamin Constant</t>
+          <t>Francis Pretty</t>
         </is>
       </c>
       <c r="B163">
-        <v>0.8719499678946409</v>
+        <v>0.9010712381421834</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Aeschylus</t>
+          <t>Cellini</t>
         </is>
       </c>
       <c r="B164">
-        <v>0.8686422819033458</v>
+        <v>0.9001306112624604</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Wollstonecraft</t>
+          <t>David Ricardo</t>
         </is>
       </c>
       <c r="B165">
-        <v>0.8666110707665654</v>
+        <v>0.8923053962556285</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Edmund Spenser</t>
+          <t>Augustine</t>
         </is>
       </c>
       <c r="B166">
-        <v>0.8490406006251188</v>
+        <v>0.89216721135571</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Hamann</t>
+          <t>Aeschylus</t>
         </is>
       </c>
       <c r="B167">
-        <v>0.8347599455435567</v>
+        <v>0.8843046206154513</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ranke</t>
+          <t>Ferdinand Lassalle</t>
         </is>
       </c>
       <c r="B168">
-        <v>0.8184964202513483</v>
+        <v>0.8779792543542712</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>Wollstonecraft</t>
         </is>
       </c>
       <c r="B169">
-        <v>0.8081005461295456</v>
+        <v>0.8734346037350291</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Helmholtz</t>
+          <t>Homer</t>
         </is>
       </c>
       <c r="B170">
-        <v>0.796588313468519</v>
+        <v>0.8680389019610801</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Pedro Calderón de la Barca</t>
+          <t>Pliny the Younger</t>
         </is>
       </c>
       <c r="B171">
-        <v>0.7733634044241829</v>
+        <v>0.8563566660553577</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Bakunin</t>
+          <t>Helmholtz</t>
         </is>
       </c>
       <c r="B172">
-        <v>0.7640745869168376</v>
+        <v>0.8334635719011914</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Henry George</t>
+          <t>Hamann</t>
         </is>
       </c>
       <c r="B173">
-        <v>0.7534386721488474</v>
+        <v>0.8248958150905679</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Thomas More</t>
+          <t>Eduard Bernstein</t>
         </is>
       </c>
       <c r="B174">
-        <v>0.7507542073632963</v>
+        <v>0.8210628593485989</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sophocles</t>
+          <t>Machiavelli</t>
         </is>
       </c>
       <c r="B175">
-        <v>0.7462045642530356</v>
+        <v>0.7687974057303174</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Friedrich Heinrich Jacobi</t>
+          <t>Hans Kelsen</t>
         </is>
       </c>
       <c r="B176">
-        <v>0.7339816701545473</v>
+        <v>0.7540246015470992</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Simmel</t>
+          <t>Ferdinand Tönnies</t>
         </is>
       </c>
       <c r="B177">
-        <v>0.7216124803660625</v>
+        <v>0.7529711002324053</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ferdinand Tönnies</t>
+          <t>Sophocles</t>
         </is>
       </c>
       <c r="B178">
-        <v>0.7194150968899609</v>
+        <v>0.7420744265583965</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Pericles</t>
+          <t>Simmel</t>
         </is>
       </c>
       <c r="B179">
-        <v>0.7099333289216239</v>
+        <v>0.7333936790485629</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Arthur Moeller van den Bruck</t>
+          <t>Friedrich Heinrich Jacobi</t>
         </is>
       </c>
       <c r="B180">
-        <v>0.7083339940803417</v>
+        <v>0.7291238847561432</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Aquinas</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="B181">
-        <v>0.6903089429197036</v>
+        <v>0.7159316312372023</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Julius Evola</t>
+          <t>Proudhon</t>
         </is>
       </c>
       <c r="B182">
-        <v>0.6844319245076712</v>
+        <v>0.7157384390580676</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Machiavelli</t>
+          <t>Julius Evola</t>
         </is>
       </c>
       <c r="B183">
-        <v>0.6508576087925289</v>
+        <v>0.7105158361823937</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Blanqui</t>
+          <t>Arthur Moeller van den Bruck</t>
         </is>
       </c>
       <c r="B184">
-        <v>0.619986439584297</v>
+        <v>0.7062799353114058</v>
       </c>
     </row>
     <row r="185">
@@ -7038,275 +7038,281 @@
         </is>
       </c>
       <c r="B185">
-        <v>0.6140113742551108</v>
+        <v>0.7022697193313883</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Hobbes</t>
+          <t>Aquinas</t>
         </is>
       </c>
       <c r="B186">
-        <v>0.5978210016853273</v>
+        <v>0.7016325024591787</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Percy Bysshe Shelley</t>
         </is>
       </c>
       <c r="B187">
-        <v>0.5875499849913329</v>
+        <v>0.6917317581855909</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Aristotle</t>
+          <t>Izaak Walton</t>
         </is>
       </c>
       <c r="B188">
-        <v>0.5837024103533147</v>
+        <v>0.6896851377536867</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Rodbertus</t>
+          <t>Bakunin</t>
         </is>
       </c>
       <c r="B189">
-        <v>0.5724118322862386</v>
+        <v>0.6780674772489793</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Proudhon</t>
+          <t>Ranke</t>
         </is>
       </c>
       <c r="B190">
-        <v>0.5529414148966421</v>
+        <v>0.6549985791003777</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Friedrich List</t>
+          <t>Blanqui</t>
         </is>
       </c>
       <c r="B191">
-        <v>0.5500357115511714</v>
+        <v>0.6412634833691779</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>William Penn</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B192">
-        <v>0.5300273425368476</v>
+        <v>0.6262918294090748</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bigges</t>
+          <t>Hobbes</t>
         </is>
       </c>
       <c r="B193">
-        <v>0.5240399083028126</v>
+        <v>0.6157201919329809</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Aristotle</t>
         </is>
       </c>
       <c r="B194">
-        <v>0.5221476033296331</v>
+        <v>0.5862017056017041</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Alexander Hamilton</t>
+          <t>Wundt</t>
         </is>
       </c>
       <c r="B195">
-        <v>0.4965311446299902</v>
+        <v>0.5832999161308772</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Walt Whitman</t>
+          <t>Rodbertus</t>
         </is>
       </c>
       <c r="B196">
-        <v>0.4782395411855079</v>
+        <v>0.5710401302772447</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Oliver Wendell Holmes</t>
+          <t>William Penn</t>
         </is>
       </c>
       <c r="B197">
-        <v>0.4571503178418703</v>
+        <v>0.5406673750116769</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Hans Christian Andersen</t>
+          <t>Bigges</t>
         </is>
       </c>
       <c r="B198">
-        <v>0.4528469925517988</v>
+        <v>0.5370122307515564</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Aristophanes</t>
+          <t>Alexander Hamilton</t>
         </is>
       </c>
       <c r="B199">
-        <v>0.3947114935724308</v>
+        <v>0.5290485726125359</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Robert Browning</t>
+          <t>Hans Christian Andersen</t>
         </is>
       </c>
       <c r="B200">
-        <v>0.3934299689375598</v>
+        <v>0.4649041133128981</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Dilthey</t>
+          <t>Oliver Wendell Holmes</t>
         </is>
       </c>
       <c r="B201">
-        <v>0.3928809919898431</v>
+        <v>0.4648402092526129</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Charles Darwin</t>
+          <t>Tacitus</t>
         </is>
       </c>
       <c r="B202">
-        <v>0.3636745867747841</v>
+        <v>0.4533595217650155</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Chaucer</t>
+          <t>Goethe</t>
         </is>
       </c>
       <c r="B203">
-        <v>0.3534481190918053</v>
+        <v>0.4445268304811755</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Goethe</t>
+          <t>Walt Whitman</t>
         </is>
       </c>
       <c r="B204">
-        <v>0.3504715355612631</v>
+        <v>0.4395239898089393</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Plato</t>
+          <t>Charles Darwin</t>
         </is>
       </c>
       <c r="B205">
-        <v>0.3470342986835367</v>
+        <v>0.4005459218939073</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Percy Bysshe Shelley</t>
+          <t>Dilthey</t>
         </is>
       </c>
       <c r="B206">
-        <v>0.3431153622617861</v>
+        <v>0.3920911604813025</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Henry Fielding</t>
+          <t>Chaucer</t>
         </is>
       </c>
       <c r="B207">
-        <v>0.3201665987865554</v>
+        <v>0.3532053100740929</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Dante Alighieri</t>
-        </is>
+          <t>Plato</t>
+        </is>
+      </c>
+      <c r="B208">
+        <v>0.3517443996423377</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Frederick Douglass</t>
-        </is>
+          <t>Henry Fielding</t>
+        </is>
+      </c>
+      <c r="B209">
+        <v>0.3166661816090833</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>Dante Alighieri</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Edmund Spenser</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Marlowe</t>
+          <t>Herodotus</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Pasteur</t>
+          <t>Marlowe</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Tacitus</t>
+          <t>Pasteur</t>
         </is>
       </c>
     </row>
